--- a/data/WP17_sachgebiete_GRÜNE.xlsx
+++ b/data/WP17_sachgebiete_GRÜNE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t xml:space="preserve">Sachgebiet</t>
   </si>
@@ -27,9 +27,6 @@
   </si>
   <si>
     <t xml:space="preserve">Verspätet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pünktlichkeitsquote</t>
   </si>
   <si>
     <t xml:space="preserve">Informations- und Kommunikationstechnologien</t>
@@ -782,13 +779,10 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
         <v>17</v>
@@ -802,13 +796,10 @@
       <c r="E2" t="n">
         <v>103</v>
       </c>
-      <c r="F2" t="n">
-        <v>24.2647058823529</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
         <v>17</v>
@@ -822,13 +813,10 @@
       <c r="E3" t="n">
         <v>69</v>
       </c>
-      <c r="F3" t="n">
-        <v>37.8378378378378</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
         <v>17</v>
@@ -842,13 +830,10 @@
       <c r="E4" t="n">
         <v>75</v>
       </c>
-      <c r="F4" t="n">
-        <v>31.8181818181818</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
         <v>17</v>
@@ -862,13 +847,10 @@
       <c r="E5" t="n">
         <v>60</v>
       </c>
-      <c r="F5" t="n">
-        <v>38.7755102040816</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
         <v>17</v>
@@ -882,13 +864,10 @@
       <c r="E6" t="n">
         <v>55</v>
       </c>
-      <c r="F6" t="n">
-        <v>43.298969072165</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>17</v>
@@ -902,13 +881,10 @@
       <c r="E7" t="n">
         <v>82</v>
       </c>
-      <c r="F7" t="n">
-        <v>15.4639175257732</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
         <v>17</v>
@@ -922,13 +898,10 @@
       <c r="E8" t="n">
         <v>76</v>
       </c>
-      <c r="F8" t="n">
-        <v>11.6279069767442</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>17</v>
@@ -942,13 +915,10 @@
       <c r="E9" t="n">
         <v>40</v>
       </c>
-      <c r="F9" t="n">
-        <v>50.6172839506173</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n">
         <v>17</v>
@@ -962,13 +932,10 @@
       <c r="E10" t="n">
         <v>50</v>
       </c>
-      <c r="F10" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
         <v>17</v>
@@ -982,13 +949,10 @@
       <c r="E11" t="n">
         <v>36</v>
       </c>
-      <c r="F11" t="n">
-        <v>52</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
         <v>17</v>
@@ -1002,13 +966,10 @@
       <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="n">
-        <v>90.4109589041096</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n">
         <v>17</v>
@@ -1022,13 +983,10 @@
       <c r="E13" t="n">
         <v>50</v>
       </c>
-      <c r="F13" t="n">
-        <v>28.5714285714286</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n">
         <v>17</v>
@@ -1042,13 +1000,10 @@
       <c r="E14" t="n">
         <v>44</v>
       </c>
-      <c r="F14" t="n">
-        <v>36.231884057971</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n">
         <v>17</v>
@@ -1062,13 +1017,10 @@
       <c r="E15" t="n">
         <v>20</v>
       </c>
-      <c r="F15" t="n">
-        <v>69.2307692307692</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>17</v>
@@ -1082,13 +1034,10 @@
       <c r="E16" t="n">
         <v>44</v>
       </c>
-      <c r="F16" t="n">
-        <v>31.25</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n">
         <v>17</v>
@@ -1102,13 +1051,10 @@
       <c r="E17" t="n">
         <v>47</v>
       </c>
-      <c r="F17" t="n">
-        <v>26.5625</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n">
         <v>17</v>
@@ -1122,13 +1068,10 @@
       <c r="E18" t="n">
         <v>42</v>
       </c>
-      <c r="F18" t="n">
-        <v>19.2307692307692</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n">
         <v>17</v>
@@ -1142,13 +1085,10 @@
       <c r="E19" t="n">
         <v>36</v>
       </c>
-      <c r="F19" t="n">
-        <v>30.7692307692308</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n">
         <v>17</v>
@@ -1162,13 +1102,10 @@
       <c r="E20" t="n">
         <v>17</v>
       </c>
-      <c r="F20" t="n">
-        <v>62.2222222222222</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n">
         <v>17</v>
@@ -1182,13 +1119,10 @@
       <c r="E21" t="n">
         <v>16</v>
       </c>
-      <c r="F21" t="n">
-        <v>61.9047619047619</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n">
         <v>17</v>
@@ -1202,13 +1136,10 @@
       <c r="E22" t="n">
         <v>23</v>
       </c>
-      <c r="F22" t="n">
-        <v>45.2380952380952</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n">
         <v>17</v>
@@ -1222,13 +1153,10 @@
       <c r="E23" t="n">
         <v>38</v>
       </c>
-      <c r="F23" t="n">
-        <v>9.52380952380952</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n">
         <v>17</v>
@@ -1242,13 +1170,10 @@
       <c r="E24" t="n">
         <v>23</v>
       </c>
-      <c r="F24" t="n">
-        <v>39.4736842105263</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n">
         <v>17</v>
@@ -1262,13 +1187,10 @@
       <c r="E25" t="n">
         <v>21</v>
       </c>
-      <c r="F25" t="n">
-        <v>43.2432432432432</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n">
         <v>17</v>
@@ -1282,13 +1204,10 @@
       <c r="E26" t="n">
         <v>22</v>
       </c>
-      <c r="F26" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n">
         <v>17</v>
@@ -1302,13 +1221,10 @@
       <c r="E27" t="n">
         <v>25</v>
       </c>
-      <c r="F27" t="n">
-        <v>24.2424242424242</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n">
         <v>17</v>
@@ -1322,13 +1238,10 @@
       <c r="E28" t="n">
         <v>16</v>
       </c>
-      <c r="F28" t="n">
-        <v>48.3870967741936</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n">
         <v>17</v>
@@ -1342,13 +1255,10 @@
       <c r="E29" t="n">
         <v>27</v>
       </c>
-      <c r="F29" t="n">
-        <v>12.9032258064516</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n">
         <v>17</v>
@@ -1362,13 +1272,10 @@
       <c r="E30" t="n">
         <v>15</v>
       </c>
-      <c r="F30" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n">
         <v>17</v>
@@ -1382,13 +1289,10 @@
       <c r="E31" t="n">
         <v>21</v>
       </c>
-      <c r="F31" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n">
         <v>17</v>
@@ -1402,13 +1306,10 @@
       <c r="E32" t="n">
         <v>26</v>
       </c>
-      <c r="F32" t="n">
-        <v>7.14285714285714</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n">
         <v>17</v>
@@ -1422,13 +1323,10 @@
       <c r="E33" t="n">
         <v>14</v>
       </c>
-      <c r="F33" t="n">
-        <v>46.1538461538462</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n">
         <v>17</v>
@@ -1442,13 +1340,10 @@
       <c r="E34" t="n">
         <v>18</v>
       </c>
-      <c r="F34" t="n">
-        <v>28</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n">
         <v>17</v>
@@ -1462,13 +1357,10 @@
       <c r="E35" t="n">
         <v>20</v>
       </c>
-      <c r="F35" t="n">
-        <v>13.0434782608696</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n">
         <v>17</v>
@@ -1482,13 +1374,10 @@
       <c r="E36" t="n">
         <v>14</v>
       </c>
-      <c r="F36" t="n">
-        <v>39.1304347826087</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n">
         <v>17</v>
@@ -1502,13 +1391,10 @@
       <c r="E37" t="n">
         <v>19</v>
       </c>
-      <c r="F37" t="n">
-        <v>13.6363636363636</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n">
         <v>17</v>
@@ -1522,13 +1408,10 @@
       <c r="E38" t="n">
         <v>22</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n">
         <v>17</v>
@@ -1542,13 +1425,10 @@
       <c r="E39" t="n">
         <v>15</v>
       </c>
-      <c r="F39" t="n">
-        <v>28.5714285714286</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n">
         <v>17</v>
@@ -1562,13 +1442,10 @@
       <c r="E40" t="n">
         <v>14</v>
       </c>
-      <c r="F40" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n">
         <v>17</v>
@@ -1582,13 +1459,10 @@
       <c r="E41" t="n">
         <v>13</v>
       </c>
-      <c r="F41" t="n">
-        <v>38.0952380952381</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n">
         <v>17</v>
@@ -1602,13 +1476,10 @@
       <c r="E42" t="n">
         <v>11</v>
       </c>
-      <c r="F42" t="n">
-        <v>42.1052631578947</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n">
         <v>17</v>
@@ -1622,13 +1493,10 @@
       <c r="E43" t="n">
         <v>9</v>
       </c>
-      <c r="F43" t="n">
-        <v>52.6315789473684</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n">
         <v>17</v>
@@ -1642,13 +1510,10 @@
       <c r="E44" t="n">
         <v>13</v>
       </c>
-      <c r="F44" t="n">
-        <v>27.7777777777778</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n">
         <v>17</v>
@@ -1662,13 +1527,10 @@
       <c r="E45" t="n">
         <v>9</v>
       </c>
-      <c r="F45" t="n">
-        <v>47.0588235294118</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n">
         <v>17</v>
@@ -1682,13 +1544,10 @@
       <c r="E46" t="n">
         <v>11</v>
       </c>
-      <c r="F46" t="n">
-        <v>31.25</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n">
         <v>17</v>
@@ -1702,13 +1561,10 @@
       <c r="E47" t="n">
         <v>8</v>
       </c>
-      <c r="F47" t="n">
-        <v>42.8571428571429</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n">
         <v>17</v>
@@ -1722,13 +1578,10 @@
       <c r="E48" t="n">
         <v>1</v>
       </c>
-      <c r="F48" t="n">
-        <v>92.8571428571429</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n">
         <v>17</v>
@@ -1742,13 +1595,10 @@
       <c r="E49" t="n">
         <v>11</v>
       </c>
-      <c r="F49" t="n">
-        <v>15.3846153846154</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n">
         <v>17</v>
@@ -1762,13 +1612,10 @@
       <c r="E50" t="n">
         <v>9</v>
       </c>
-      <c r="F50" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n">
         <v>17</v>
@@ -1782,13 +1629,10 @@
       <c r="E51" t="n">
         <v>6</v>
       </c>
-      <c r="F51" t="n">
-        <v>45.4545454545455</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n">
         <v>17</v>
@@ -1802,13 +1646,10 @@
       <c r="E52" t="n">
         <v>7</v>
       </c>
-      <c r="F52" t="n">
-        <v>36.3636363636364</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n">
         <v>17</v>
@@ -1822,13 +1663,10 @@
       <c r="E53" t="n">
         <v>3</v>
       </c>
-      <c r="F53" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n">
         <v>17</v>
@@ -1842,13 +1680,10 @@
       <c r="E54" t="n">
         <v>8</v>
       </c>
-      <c r="F54" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n">
         <v>17</v>
@@ -1862,13 +1697,10 @@
       <c r="E55" t="n">
         <v>9</v>
       </c>
-      <c r="F55" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n">
         <v>17</v>
@@ -1882,13 +1714,10 @@
       <c r="E56" t="n">
         <v>8</v>
       </c>
-      <c r="F56" t="n">
-        <v>11.1111111111111</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n">
         <v>17</v>
@@ -1902,13 +1731,10 @@
       <c r="E57" t="n">
         <v>5</v>
       </c>
-      <c r="F57" t="n">
-        <v>44.4444444444444</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n">
         <v>17</v>
@@ -1922,13 +1748,10 @@
       <c r="E58" t="n">
         <v>5</v>
       </c>
-      <c r="F58" t="n">
-        <v>37.5</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n">
         <v>17</v>
@@ -1942,13 +1765,10 @@
       <c r="E59" t="n">
         <v>5</v>
       </c>
-      <c r="F59" t="n">
-        <v>37.5</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n">
         <v>17</v>
@@ -1962,13 +1782,10 @@
       <c r="E60" t="n">
         <v>4</v>
       </c>
-      <c r="F60" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n">
         <v>17</v>
@@ -1982,13 +1799,10 @@
       <c r="E61" t="n">
         <v>5</v>
       </c>
-      <c r="F61" t="n">
-        <v>37.5</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n">
         <v>17</v>
@@ -2002,13 +1816,10 @@
       <c r="E62" t="n">
         <v>4</v>
       </c>
-      <c r="F62" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n">
         <v>17</v>
@@ -2022,13 +1833,10 @@
       <c r="E63" t="n">
         <v>6</v>
       </c>
-      <c r="F63" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n">
         <v>17</v>
@@ -2042,13 +1850,10 @@
       <c r="E64" t="n">
         <v>4</v>
       </c>
-      <c r="F64" t="n">
-        <v>42.8571428571429</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n">
         <v>17</v>
@@ -2062,13 +1867,10 @@
       <c r="E65" t="n">
         <v>7</v>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n">
         <v>17</v>
@@ -2082,13 +1884,10 @@
       <c r="E66" t="n">
         <v>6</v>
       </c>
-      <c r="F66" t="n">
-        <v>14.2857142857143</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n">
         <v>17</v>
@@ -2102,13 +1901,10 @@
       <c r="E67" t="n">
         <v>2</v>
       </c>
-      <c r="F67" t="n">
-        <v>71.4285714285714</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n">
         <v>17</v>
@@ -2122,13 +1918,10 @@
       <c r="E68" t="n">
         <v>4</v>
       </c>
-      <c r="F68" t="n">
-        <v>42.8571428571429</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n">
         <v>17</v>
@@ -2142,13 +1935,10 @@
       <c r="E69" t="n">
         <v>3</v>
       </c>
-      <c r="F69" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n">
         <v>17</v>
@@ -2162,13 +1952,10 @@
       <c r="E70" t="n">
         <v>5</v>
       </c>
-      <c r="F70" t="n">
-        <v>16.6666666666667</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n">
         <v>17</v>
@@ -2182,13 +1969,10 @@
       <c r="E71" t="n">
         <v>5</v>
       </c>
-      <c r="F71" t="n">
-        <v>16.6666666666667</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n">
         <v>17</v>
@@ -2202,13 +1986,10 @@
       <c r="E72" t="n">
         <v>3</v>
       </c>
-      <c r="F72" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n">
         <v>17</v>
@@ -2222,13 +2003,10 @@
       <c r="E73" t="n">
         <v>6</v>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n">
         <v>17</v>
@@ -2242,13 +2020,10 @@
       <c r="E74" t="n">
         <v>6</v>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n">
         <v>17</v>
@@ -2262,13 +2037,10 @@
       <c r="E75" t="n">
         <v>1</v>
       </c>
-      <c r="F75" t="n">
-        <v>83.3333333333333</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n">
         <v>17</v>
@@ -2282,13 +2054,10 @@
       <c r="E76" t="n">
         <v>6</v>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n">
         <v>17</v>
@@ -2302,13 +2071,10 @@
       <c r="E77" t="n">
         <v>2</v>
       </c>
-      <c r="F77" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n">
         <v>17</v>
@@ -2322,13 +2088,10 @@
       <c r="E78" t="n">
         <v>4</v>
       </c>
-      <c r="F78" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n">
         <v>17</v>
@@ -2342,13 +2105,10 @@
       <c r="E79" t="n">
         <v>5</v>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n">
         <v>17</v>
@@ -2362,13 +2122,10 @@
       <c r="E80" t="n">
         <v>2</v>
       </c>
-      <c r="F80" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n">
         <v>17</v>
@@ -2382,13 +2139,10 @@
       <c r="E81" t="n">
         <v>3</v>
       </c>
-      <c r="F81" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n">
         <v>17</v>
@@ -2402,13 +2156,10 @@
       <c r="E82" t="n">
         <v>2</v>
       </c>
-      <c r="F82" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n">
         <v>17</v>
@@ -2422,13 +2173,10 @@
       <c r="E83" t="n">
         <v>4</v>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n">
         <v>17</v>
@@ -2442,13 +2190,10 @@
       <c r="E84" t="n">
         <v>2</v>
       </c>
-      <c r="F84" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n">
         <v>17</v>
@@ -2462,13 +2207,10 @@
       <c r="E85" t="n">
         <v>3</v>
       </c>
-      <c r="F85" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n">
         <v>17</v>
@@ -2482,13 +2224,10 @@
       <c r="E86" t="n">
         <v>2</v>
       </c>
-      <c r="F86" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n">
         <v>17</v>
@@ -2502,13 +2241,10 @@
       <c r="E87" t="n">
         <v>0</v>
       </c>
-      <c r="F87" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n">
         <v>17</v>
@@ -2522,13 +2258,10 @@
       <c r="E88" t="n">
         <v>4</v>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n">
         <v>17</v>
@@ -2542,13 +2275,10 @@
       <c r="E89" t="n">
         <v>2</v>
       </c>
-      <c r="F89" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B90" t="n">
         <v>17</v>
@@ -2562,13 +2292,10 @@
       <c r="E90" t="n">
         <v>4</v>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B91" t="n">
         <v>17</v>
@@ -2582,13 +2309,10 @@
       <c r="E91" t="n">
         <v>4</v>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92" t="n">
         <v>17</v>
@@ -2602,13 +2326,10 @@
       <c r="E92" t="n">
         <v>2</v>
       </c>
-      <c r="F92" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93" t="n">
         <v>17</v>
@@ -2622,13 +2343,10 @@
       <c r="E93" t="n">
         <v>0</v>
       </c>
-      <c r="F93" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94" t="n">
         <v>17</v>
@@ -2642,13 +2360,10 @@
       <c r="E94" t="n">
         <v>0</v>
       </c>
-      <c r="F94" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95" t="n">
         <v>17</v>
@@ -2662,13 +2377,10 @@
       <c r="E95" t="n">
         <v>3</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" t="n">
         <v>17</v>
@@ -2682,13 +2394,10 @@
       <c r="E96" t="n">
         <v>1</v>
       </c>
-      <c r="F96" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" t="n">
         <v>17</v>
@@ -2702,13 +2411,10 @@
       <c r="E97" t="n">
         <v>2</v>
       </c>
-      <c r="F97" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98" t="n">
         <v>17</v>
@@ -2722,13 +2428,10 @@
       <c r="E98" t="n">
         <v>0</v>
       </c>
-      <c r="F98" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" t="n">
         <v>17</v>
@@ -2742,13 +2445,10 @@
       <c r="E99" t="n">
         <v>1</v>
       </c>
-      <c r="F99" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100" t="n">
         <v>17</v>
@@ -2762,13 +2462,10 @@
       <c r="E100" t="n">
         <v>1</v>
       </c>
-      <c r="F100" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B101" t="n">
         <v>17</v>
@@ -2782,13 +2479,10 @@
       <c r="E101" t="n">
         <v>3</v>
       </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B102" t="n">
         <v>17</v>
@@ -2802,13 +2496,10 @@
       <c r="E102" t="n">
         <v>1</v>
       </c>
-      <c r="F102" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103" t="n">
         <v>17</v>
@@ -2822,13 +2513,10 @@
       <c r="E103" t="n">
         <v>2</v>
       </c>
-      <c r="F103" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104" t="n">
         <v>17</v>
@@ -2842,13 +2530,10 @@
       <c r="E104" t="n">
         <v>1</v>
       </c>
-      <c r="F104" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105" t="n">
         <v>17</v>
@@ -2862,13 +2547,10 @@
       <c r="E105" t="n">
         <v>2</v>
       </c>
-      <c r="F105" t="n">
-        <v>33.3333333333333</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106" t="n">
         <v>17</v>
@@ -2882,13 +2564,10 @@
       <c r="E106" t="n">
         <v>3</v>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" t="n">
         <v>17</v>
@@ -2902,13 +2581,10 @@
       <c r="E107" t="n">
         <v>1</v>
       </c>
-      <c r="F107" t="n">
-        <v>66.6666666666667</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108" t="n">
         <v>17</v>
@@ -2922,13 +2598,10 @@
       <c r="E108" t="n">
         <v>1</v>
       </c>
-      <c r="F108" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109" t="n">
         <v>17</v>
@@ -2942,13 +2615,10 @@
       <c r="E109" t="n">
         <v>0</v>
       </c>
-      <c r="F109" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110" t="n">
         <v>17</v>
@@ -2962,13 +2632,10 @@
       <c r="E110" t="n">
         <v>1</v>
       </c>
-      <c r="F110" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111" t="n">
         <v>17</v>
@@ -2982,13 +2649,10 @@
       <c r="E111" t="n">
         <v>2</v>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B112" t="n">
         <v>17</v>
@@ -3002,13 +2666,10 @@
       <c r="E112" t="n">
         <v>2</v>
       </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B113" t="n">
         <v>17</v>
@@ -3022,13 +2683,10 @@
       <c r="E113" t="n">
         <v>2</v>
       </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B114" t="n">
         <v>17</v>
@@ -3042,13 +2700,10 @@
       <c r="E114" t="n">
         <v>2</v>
       </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B115" t="n">
         <v>17</v>
@@ -3062,13 +2717,10 @@
       <c r="E115" t="n">
         <v>1</v>
       </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B116" t="n">
         <v>17</v>
@@ -3082,13 +2734,10 @@
       <c r="E116" t="n">
         <v>1</v>
       </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B117" t="n">
         <v>17</v>
@@ -3102,13 +2751,10 @@
       <c r="E117" t="n">
         <v>0</v>
       </c>
-      <c r="F117" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B118" t="n">
         <v>17</v>
@@ -3122,13 +2768,10 @@
       <c r="E118" t="n">
         <v>1</v>
       </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B119" t="n">
         <v>17</v>
@@ -3142,13 +2785,10 @@
       <c r="E119" t="n">
         <v>1</v>
       </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B120" t="n">
         <v>17</v>
@@ -3162,13 +2802,10 @@
       <c r="E120" t="n">
         <v>0</v>
       </c>
-      <c r="F120" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B121" t="n">
         <v>17</v>
@@ -3182,13 +2819,10 @@
       <c r="E121" t="n">
         <v>1</v>
       </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B122" t="n">
         <v>17</v>
@@ -3202,13 +2836,10 @@
       <c r="E122" t="n">
         <v>1</v>
       </c>
-      <c r="F122" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B123" t="n">
         <v>17</v>
@@ -3222,13 +2853,10 @@
       <c r="E123" t="n">
         <v>1</v>
       </c>
-      <c r="F123" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B124" t="n">
         <v>17</v>
@@ -3242,13 +2870,10 @@
       <c r="E124" t="n">
         <v>0</v>
       </c>
-      <c r="F124" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B125" t="n">
         <v>17</v>
@@ -3262,13 +2887,10 @@
       <c r="E125" t="n">
         <v>0</v>
       </c>
-      <c r="F125" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B126" t="n">
         <v>17</v>
@@ -3282,13 +2904,10 @@
       <c r="E126" t="n">
         <v>0</v>
       </c>
-      <c r="F126" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B127" t="n">
         <v>17</v>
@@ -3302,13 +2921,10 @@
       <c r="E127" t="n">
         <v>1</v>
       </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B128" t="n">
         <v>17</v>
@@ -3322,13 +2938,10 @@
       <c r="E128" t="n">
         <v>1</v>
       </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B129" t="n">
         <v>17</v>
@@ -3342,13 +2955,10 @@
       <c r="E129" t="n">
         <v>0</v>
       </c>
-      <c r="F129" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B130" t="n">
         <v>17</v>
@@ -3362,13 +2972,10 @@
       <c r="E130" t="n">
         <v>0</v>
       </c>
-      <c r="F130" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B131" t="n">
         <v>17</v>
@@ -3382,13 +2989,10 @@
       <c r="E131" t="n">
         <v>1</v>
       </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B132" t="n">
         <v>17</v>
@@ -3402,13 +3006,10 @@
       <c r="E132" t="n">
         <v>1</v>
       </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B133" t="n">
         <v>17</v>
@@ -3422,13 +3023,10 @@
       <c r="E133" t="n">
         <v>1</v>
       </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B134" t="n">
         <v>17</v>
@@ -3442,13 +3040,10 @@
       <c r="E134" t="n">
         <v>0</v>
       </c>
-      <c r="F134" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B135" t="n">
         <v>17</v>
@@ -3462,13 +3057,10 @@
       <c r="E135" t="n">
         <v>1</v>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B136" t="n">
         <v>17</v>
@@ -3482,13 +3074,10 @@
       <c r="E136" t="n">
         <v>1</v>
       </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B137" t="n">
         <v>17</v>
@@ -3501,9 +3090,6 @@
       </c>
       <c r="E137" t="n">
         <v>1</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3740,13 +3326,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90684FF7-052F-4E83-AD83-21F898EA76A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50743FF8-9790-4C25-9F27-680443C17741}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8955839-0C0B-453F-9358-7FC0DBCED372}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BA1ACB9-8CCF-410F-AD89-226C178DFD28}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDDCB936-DD38-4EDF-9F3C-9B0A8176049E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC578F90-FF1F-4B49-9E67-3C8D1806E4B7}"/>
 </file>